--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128268565</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547714</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6321748</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>128268565</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,7 +814,7 @@
         <v>128268565</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,6 +931,129 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128582274</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>547688</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321677</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,129 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128626903</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547621</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6321795</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>128582274</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>128626903</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>128268565</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>128582274</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>128626903</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>128268565</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>128582274</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>128626903</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40182-2025 artfynd.xlsx
+++ b/artfynd/A 40182-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>128582274</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>128626903</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
